--- a/원본데이터/처방현황_260619.xlsx
+++ b/원본데이터/처방현황_260619.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="117">
   <si>
     <t>등록번호</t>
   </si>
@@ -399,6 +399,9 @@
   <si>
     <t>E6544</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Hicardi)Bed side monitoring(1일당)</t>
   </si>
 </sst>
 </file>
@@ -481,7 +484,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -512,7 +515,22 @@
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -525,7 +543,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -535,9 +553,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -546,6 +561,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -833,13 +854,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
@@ -876,12 +897,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>78</v>
+    <row r="2" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C2" t="s">
         <v>115</v>
@@ -923,12 +944,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>78</v>
+    <row r="3" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C3" t="s">
         <v>115</v>
@@ -970,12 +991,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>78</v>
+    <row r="4" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C4" t="s">
         <v>115</v>
@@ -1017,12 +1038,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>78</v>
+    <row r="5" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C5" t="s">
         <v>115</v>
@@ -1064,12 +1085,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>78</v>
+    <row r="6" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C6" t="s">
         <v>115</v>
@@ -1111,12 +1132,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>78</v>
+    <row r="7" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C7" t="s">
         <v>115</v>
@@ -1158,12 +1179,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
+    <row r="8" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>115</v>
@@ -1205,12 +1226,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>78</v>
+    <row r="9" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C9" t="s">
         <v>115</v>
@@ -1252,12 +1273,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>78</v>
+    <row r="10" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C10" t="s">
         <v>115</v>
@@ -1299,12 +1320,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
+    <row r="11" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C11" t="s">
         <v>115</v>
@@ -1346,12 +1367,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>78</v>
+    <row r="12" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
@@ -1393,12 +1414,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>78</v>
+    <row r="13" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>115</v>
@@ -1440,12 +1461,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>78</v>
+    <row r="14" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C14" t="s">
         <v>115</v>
@@ -1487,12 +1508,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>78</v>
+    <row r="15" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C15" t="s">
         <v>115</v>
@@ -1534,12 +1555,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>78</v>
+    <row r="16" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C16" t="s">
         <v>115</v>
@@ -1581,12 +1602,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>78</v>
+    <row r="17" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
@@ -1628,12 +1649,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>78</v>
+    <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C18" t="s">
         <v>115</v>
@@ -1675,12 +1696,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>78</v>
+    <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C19" t="s">
         <v>115</v>
@@ -1722,12 +1743,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>78</v>
+    <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C20" t="s">
         <v>115</v>
@@ -1769,12 +1790,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>78</v>
+    <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C21" t="s">
         <v>115</v>
@@ -1816,12 +1837,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>78</v>
+    <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
@@ -1863,12 +1884,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>78</v>
+    <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C23" t="s">
         <v>115</v>
@@ -1910,12 +1931,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>78</v>
+    <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C24" t="s">
         <v>115</v>
@@ -1957,12 +1978,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>78</v>
+    <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C25" t="s">
         <v>115</v>
@@ -2004,12 +2025,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>78</v>
+    <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C26" t="s">
         <v>115</v>
@@ -2051,12 +2072,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>78</v>
+    <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C27" t="s">
         <v>115</v>
@@ -2098,12 +2119,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>78</v>
+    <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
@@ -2145,12 +2166,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>78</v>
+    <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C29" t="s">
         <v>115</v>
@@ -2192,12 +2213,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>78</v>
+    <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C30" t="s">
         <v>115</v>
@@ -2239,12 +2260,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>78</v>
+    <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C31" t="s">
         <v>115</v>
@@ -2286,12 +2307,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>78</v>
+    <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C32" t="s">
         <v>115</v>
@@ -2333,12 +2354,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>78</v>
+    <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C33" t="s">
         <v>115</v>
@@ -2380,12 +2401,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>78</v>
+    <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -2427,12 +2448,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>78</v>
+    <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C35" t="s">
         <v>115</v>
@@ -2474,12 +2495,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>78</v>
+    <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C36" t="s">
         <v>115</v>
@@ -2521,12 +2542,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>78</v>
+    <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C37" t="s">
         <v>115</v>
@@ -2568,12 +2589,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>78</v>
+    <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C38" t="s">
         <v>115</v>
@@ -2615,12 +2636,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>78</v>
+    <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C39" t="s">
         <v>115</v>
@@ -2662,12 +2683,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>78</v>
+    <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C40" t="s">
         <v>115</v>
@@ -2709,12 +2730,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>78</v>
+    <row r="41" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C41" t="s">
         <v>115</v>
@@ -2756,12 +2777,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>78</v>
+    <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C42" t="s">
         <v>115</v>
@@ -2803,12 +2824,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>78</v>
+    <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C43" t="s">
         <v>115</v>
@@ -2850,12 +2871,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>78</v>
+    <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C44" t="s">
         <v>115</v>
@@ -2897,12 +2918,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>78</v>
+    <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C45" t="s">
         <v>115</v>
@@ -2944,12 +2965,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>78</v>
+    <row r="46" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C46" t="s">
         <v>115</v>
@@ -2991,12 +3012,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>78</v>
+    <row r="47" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C47" t="s">
         <v>115</v>
@@ -3038,12 +3059,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>78</v>
+    <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C48" t="s">
         <v>115</v>
@@ -3085,12 +3106,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>78</v>
+    <row r="49" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C49" t="s">
         <v>115</v>
@@ -3132,12 +3153,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>78</v>
+    <row r="50" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C50" t="s">
         <v>115</v>
@@ -3179,12 +3200,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>78</v>
+    <row r="51" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C51" t="s">
         <v>115</v>
@@ -3226,12 +3247,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>78</v>
+    <row r="52" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C52" t="s">
         <v>115</v>
@@ -3273,12 +3294,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>78</v>
+    <row r="53" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C53" t="s">
         <v>115</v>
@@ -3320,12 +3341,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>78</v>
+    <row r="54" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C54" t="s">
         <v>115</v>
@@ -3367,12 +3388,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>78</v>
+    <row r="55" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C55" t="s">
         <v>115</v>
@@ -3414,12 +3435,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>78</v>
+    <row r="56" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C56" t="s">
         <v>115</v>
@@ -3462,16 +3483,16 @@
       </c>
     </row>
     <row r="57" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>78</v>
+      <c r="A57" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C57" t="s">
         <v>115</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>883671</v>
       </c>
       <c r="E57" t="s">
@@ -3508,12 +3529,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>78</v>
+    <row r="58" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C58" t="s">
         <v>115</v>
@@ -3555,12 +3576,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>78</v>
+    <row r="59" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C59" t="s">
         <v>115</v>
@@ -3602,12 +3623,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>78</v>
+    <row r="60" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C60" t="s">
         <v>115</v>
@@ -3649,12 +3670,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>78</v>
+    <row r="61" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>116</v>
       </c>
       <c r="C61" t="s">
         <v>115</v>
